--- a/Data/Masters_programs.xlsx
+++ b/Data/Masters_programs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mustafa Ansari\Downloads\Capestone_project_AI\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453715F4-8F26-4777-BC43-5ED726A374E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90F1CB7-9940-4EFB-A7B0-42BC7ECD4A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B2779126-D451-4462-A64B-8E3CADC5287E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="88">
   <si>
     <t>Program_name</t>
   </si>
@@ -248,9 +248,6 @@
     <t>Data Science for Society and Business (Online) | Constructor University</t>
   </si>
   <si>
-    <t>Fees_per_semester_euro</t>
-  </si>
-  <si>
     <t>On-campus_accommodation_fee_euro</t>
   </si>
   <si>
@@ -298,6 +295,12 @@
   <si>
     <t>on_compus</t>
   </si>
+  <si>
+    <t>DET_MSC_online</t>
+  </si>
+  <si>
+    <t>Tuition_fees_per_semester_euro</t>
+  </si>
 </sst>
 </file>
 
@@ -337,7 +340,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -360,12 +363,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -390,6 +404,9 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -738,6 +755,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="64" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -760,13 +780,13 @@
         <v>5</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>6</v>
@@ -811,7 +831,7 @@
         <v>19</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>20</v>
@@ -843,7 +863,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2">
         <v>2</v>
@@ -935,7 +955,7 @@
         <v>27</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G3" s="2">
         <v>2</v>
@@ -1027,7 +1047,7 @@
         <v>27</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G4" s="2">
         <v>2</v>
@@ -1119,7 +1139,7 @@
         <v>27</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G5" s="2">
         <v>2</v>
@@ -1211,7 +1231,7 @@
         <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G6" s="2">
         <v>2</v>
@@ -1303,7 +1323,7 @@
         <v>27</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G7" s="2">
         <v>2</v>
@@ -1395,7 +1415,7 @@
         <v>27</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -1487,7 +1507,7 @@
         <v>59</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G9" s="2">
         <v>2</v>
@@ -1579,7 +1599,7 @@
         <v>59</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
@@ -1748,7 +1768,7 @@
     </row>
     <row r="12" spans="1:30" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>66</v>
@@ -1839,8 +1859,8 @@
       </c>
     </row>
     <row r="13" spans="1:30" ht="160" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
-        <v>85</v>
+      <c r="A13" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>43</v>
